--- a/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
@@ -1,43 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_Evidence" sheetId="1" r:id="R4d19ed3b030d43b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_INDEX" sheetId="2" r:id="R6781c9addea343bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="3" r:id="Redaaccb598824424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_入力フロー" sheetId="4" r:id="R091c4dec0e234b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_取替方式" sheetId="5" r:id="R49f0c6447b4a4b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_仕様区分" sheetId="6" r:id="R871aede2438e425d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_窓種" sheetId="7" r:id="R30b453c42af84343"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03A_枠仕様" sheetId="8" r:id="R980d7504c4cb4b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03B_窓種枠設定" sheetId="9" r:id="R6883b2dfa5cc4d07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_窓種固有仕様" sheetId="10" r:id="R62f7a893223f461e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_サイズルール" sheetId="11" r:id="Rc524d87a823d4315"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_サイズ区間" sheetId="12" r:id="R1daa7811b2e6467c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05B_境界ルール" sheetId="13" r:id="Rca4e491f34b34abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_色" sheetId="14" r:id="R451da21c560d473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06A_色適用条件" sheetId="15" r:id="R5deb7453c2cc42e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_網戸" sheetId="16" r:id="R18ab95fb2b7947c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07A_網戸適用条件" sheetId="17" r:id="Rbf917bdc50c946b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_ガラス" sheetId="18" r:id="R089cf1d2dca349a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08A_ガラス適用条件" sheetId="19" r:id="Rddcff2e65f7c4b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_その他OP" sheetId="20" r:id="R4d1140cd3e464bf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09A_OP依存関係" sheetId="21" r:id="Rca35a335935a4a37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_適用条件" sheetId="22" r:id="Rb3ce781734d24893"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10A_既設窓互換" sheetId="23" r:id="R0f812835d8ec4c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10B_現調項目" sheetId="24" r:id="R04edcb4f8a6845db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_QA" sheetId="25" r:id="R9483a120c1ce4991"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_開口構成" sheetId="26" r:id="Re73857a387d44ba3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_見積入力テスト" sheetId="27" r:id="Rbecd1f9c003f4a8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C_化粧カバー見付" sheetId="28" r:id="R2b5001b503eb4175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04B_浴室改修モード" sheetId="29" r:id="Ra92c2950c86d44f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04C_既設開口パターン" sheetId="30" r:id="R2ce09f52aa884052"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04D_開口縮小部材" sheetId="31" r:id="R8ee9478e33094889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05C_開口ポイント" sheetId="32" r:id="Rcd83cd1a5dd14240"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10D_浴室現場条件" sheetId="33" r:id="Rec47664b480e4118"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_共通参照" sheetId="34" r:id="R0e98950884a64b76"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="90_Evidence" sheetId="1" r:id="R4d19ed3b030d43b5"/>
+    <sheet name="00_INDEX" sheetId="2" r:id="R6781c9addea343bf"/>
+    <sheet name="00_README" sheetId="3" r:id="Redaaccb598824424"/>
+    <sheet name="01_入力フロー" sheetId="4" r:id="R091c4dec0e234b58"/>
+    <sheet name="02_取替方式" sheetId="5" r:id="R49f0c6447b4a4b40"/>
+    <sheet name="02A_仕様区分" sheetId="6" r:id="R871aede2438e425d"/>
+    <sheet name="03_窓種" sheetId="7" r:id="R30b453c42af84343"/>
+    <sheet name="03A_枠仕様" sheetId="8" r:id="R980d7504c4cb4b58"/>
+    <sheet name="03B_窓種枠設定" sheetId="9" r:id="R6883b2dfa5cc4d07"/>
+    <sheet name="04_窓種固有仕様" sheetId="10" r:id="R62f7a893223f461e"/>
+    <sheet name="05_サイズルール" sheetId="11" r:id="Rc524d87a823d4315"/>
+    <sheet name="05A_サイズ区間" sheetId="12" r:id="R1daa7811b2e6467c"/>
+    <sheet name="05B_境界ルール" sheetId="13" r:id="Rca4e491f34b34abc"/>
+    <sheet name="06_色" sheetId="14" r:id="R451da21c560d473b"/>
+    <sheet name="06A_色適用条件" sheetId="15" r:id="R5deb7453c2cc42e9"/>
+    <sheet name="07_網戸" sheetId="16" r:id="R18ab95fb2b7947c0"/>
+    <sheet name="07A_網戸適用条件" sheetId="17" r:id="Rbf917bdc50c946b9"/>
+    <sheet name="08_ガラス" sheetId="18" r:id="R089cf1d2dca349a4"/>
+    <sheet name="08A_ガラス適用条件" sheetId="19" r:id="Rddcff2e65f7c4b44"/>
+    <sheet name="09_その他OP" sheetId="20" r:id="R4d1140cd3e464bf8"/>
+    <sheet name="09A_OP依存関係" sheetId="21" r:id="Rca35a335935a4a37"/>
+    <sheet name="10_適用条件" sheetId="22" r:id="Rb3ce781734d24893"/>
+    <sheet name="10A_既設窓互換" sheetId="23" r:id="R0f812835d8ec4c7f"/>
+    <sheet name="10B_現調項目" sheetId="24" r:id="R04edcb4f8a6845db"/>
+    <sheet name="99_QA" sheetId="25" r:id="R9483a120c1ce4991"/>
+    <sheet name="04A_開口構成" sheetId="26" r:id="Re73857a387d44ba3"/>
+    <sheet name="11_見積入力テスト" sheetId="27" r:id="Rbecd1f9c003f4a8a"/>
+    <sheet name="10C_化粧カバー見付" sheetId="28" r:id="R2b5001b503eb4175"/>
+    <sheet name="04B_浴室改修モード" sheetId="29" r:id="Ra92c2950c86d44f5"/>
+    <sheet name="04C_既設開口パターン" sheetId="30" r:id="R2ce09f52aa884052"/>
+    <sheet name="04D_開口縮小部材" sheetId="31" r:id="R8ee9478e33094889"/>
+    <sheet name="05C_開口ポイント" sheetId="32" r:id="Rcd83cd1a5dd14240"/>
+    <sheet name="10D_浴室現場条件" sheetId="33" r:id="Rec47664b480e4118"/>
+    <sheet name="12_共通参照" sheetId="34" r:id="R0e98950884a64b76"/>
+    <sheet name="14_UI選択契約" sheetId="35" r:id="rIdReplusUiV9"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1239,6 +1240,625 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/replus-ui-v9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="184">
+        <v>リプラス住宅用・共通UI選択契約</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="186"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="str" s="181">
+        <v>分類</v>
+      </c>
+      <c r="B2" t="str" s="182">
+        <v>対象</v>
+      </c>
+      <c r="C2" t="str" s="182">
+        <v>依存元</v>
+      </c>
+      <c r="D2" t="str" s="182">
+        <v>処理</v>
+      </c>
+      <c r="E2" t="str" s="183">
+        <v>根拠区分</v>
+      </c>
+      <c r="F2" t="str">
+        <v>revision</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str" s="184">
+        <v>色連動</v>
+      </c>
+      <c r="B3" t="str" s="185">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C3" t="str" s="185">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="D3" t="str" s="185">
+        <v>{"targetField": "exterior_cover_color", "parents": ["sash_exterior_color"], "cases": [{"when": {"sash_exterior_color": "T"}, "value": "T"}, {"when": {"sash_exterior_color": "G"}, "value": "G"}, {"when": {"sash_exterior_color": "K"}, "value": "K"}, {"when": {"sash_exterior_color": "D"}, "value": "D"}, {"when": {"sash_exterior_color": "W"}, "value": "W"}], "resolvedMessage": "本体外観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E3" t="str" s="186">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F3" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str" s="184">
+        <v>色連動</v>
+      </c>
+      <c r="B4" t="str" s="185">
+        <v>interior_cover_color</v>
+      </c>
+      <c r="C4" t="str" s="185">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="D4" t="str" s="185">
+        <v>{"targetField": "interior_cover_color", "parents": ["sash_interior_color"], "cases": [{"when": {"sash_interior_color": "M"}, "value": "M"}, {"when": {"sash_interior_color": "F"}, "value": "F"}], "resolvedMessage": "本体内観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E4" t="str" s="186">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F4" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B5" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="C5" t="str" s="185"/>
+      <c r="D5" t="str" s="185">
+        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E5" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F5" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B6" t="str" s="185">
+        <v>frame_type</v>
+      </c>
+      <c r="C6" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D6" t="str" s="185">
+        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E6" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F6" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B7" t="str" s="185">
+        <v>spec_panel_configuration</v>
+      </c>
+      <c r="C7" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D7" t="str" s="185">
+        <v>{"label": "建数", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E7" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F7" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B8" t="str" s="185">
+        <v>spec_sash_configuration</v>
+      </c>
+      <c r="C8" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D8" t="str" s="185">
+        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E8" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F8" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B9" t="str" s="185">
+        <v>spec_operation_type</v>
+      </c>
+      <c r="C9" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D9" t="str" s="185">
+        <v>{"label": "操作方式", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E9" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F9" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B10" t="str" s="185">
+        <v>screen</v>
+      </c>
+      <c r="C10" t="str" s="185">
+        <v>window_type</v>
+      </c>
+      <c r="D10" t="str" s="185">
+        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
+      </c>
+      <c r="E10" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F10" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B11" t="str" s="185">
+        <v>size_mode</v>
+      </c>
+      <c r="C11" t="str" s="185"/>
+      <c r="D11" t="str" s="185">
+        <v>{"label": "寸法の指定方法", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E11" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F11" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B12" t="str" s="185">
+        <v>custom_width</v>
+      </c>
+      <c r="C12" t="str" s="185">
+        <v>size_mode</v>
+      </c>
+      <c r="D12" t="str" s="185">
+        <v>{"label": "製品仕上がり幅 W（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E12" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F12" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B13" t="str" s="185">
+        <v>custom_height</v>
+      </c>
+      <c r="C13" t="str" s="185">
+        <v>size_mode</v>
+      </c>
+      <c r="D13" t="str" s="185">
+        <v>{"label": "製品仕上がり高さ H（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E13" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F13" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B14" t="str" s="185">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="C14" t="str" s="185"/>
+      <c r="D14" t="str" s="185">
+        <v>{"label": "本体外観色", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E14" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F14" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B15" t="str" s="185">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C15" t="str" s="185">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="D15" t="str" s="185">
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E15" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F15" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B16" t="str" s="185">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="C16" t="str" s="185"/>
+      <c r="D16" t="str" s="185">
+        <v>{"label": "本体内観色", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E16" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F16" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B17" t="str" s="185">
+        <v>interior_cover_color</v>
+      </c>
+      <c r="C17" t="str" s="185">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="D17" t="str" s="185">
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E17" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F17" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B18" t="str" s="185">
+        <v>options</v>
+      </c>
+      <c r="C18" t="str" s="185"/>
+      <c r="D18" t="str" s="185">
+        <v>{"label": "追加部材・オプション", "group": "options", "internal": false}</v>
+      </c>
+      <c r="E18" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F18" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B19" t="str" s="185">
+        <v>bathroom_remodel_mode</v>
+      </c>
+      <c r="C19" t="str" s="185"/>
+      <c r="D19" t="str" s="185">
+        <v>{"label": "浴室改修モード", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E19" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F19" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B20" t="str" s="185">
+        <v>installation_region</v>
+      </c>
+      <c r="C20" t="str" s="185"/>
+      <c r="D20" t="str" s="185">
+        <v>{"label": "設置地域", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E20" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F20" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B21" t="str" s="185">
+        <v>glass_category</v>
+      </c>
+      <c r="C21" t="str" s="185">
+        <v>frame_type,installation_region,window_type</v>
+      </c>
+      <c r="D21" t="str" s="185">
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E21" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F21" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B22" t="str" s="185">
+        <v>glass</v>
+      </c>
+      <c r="C22" t="str" s="185">
+        <v>frame_type,glass_category,installation_region,window_type</v>
+      </c>
+      <c r="D22" t="str" s="185">
+        <v>{"label": "ガラス詳細・Low-E仕様", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E22" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F22" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B23" t="str" s="185">
+        <v>glass_gas</v>
+      </c>
+      <c r="C23" t="str" s="185">
+        <v>frame_type,glass_category</v>
+      </c>
+      <c r="D23" t="str" s="185">
+        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E23" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F23" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B24" t="str" s="185">
+        <v>glass_spacer</v>
+      </c>
+      <c r="C24" t="str" s="185">
+        <v>frame_type,glass_category,glass_gas</v>
+      </c>
+      <c r="D24" t="str" s="185">
+        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E24" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F24" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B25" t="str" s="185">
+        <v>bathroom_opening_pattern</v>
+      </c>
+      <c r="C25" t="str" s="185">
+        <v>bathroom_remodel_mode</v>
+      </c>
+      <c r="D25" t="str" s="185">
+        <v>{"label": "既設開口パターン", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E25" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F25" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B26" t="str" s="185">
+        <v>glass_function</v>
+      </c>
+      <c r="C26" t="str" s="185">
+        <v>glass_category,glass,window_type</v>
+      </c>
+      <c r="D26" t="str" s="185">
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E26" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F26" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B27" t="str" s="185">
+        <v>glass_appearance</v>
+      </c>
+      <c r="C27" t="str" s="185">
+        <v>glass,glass_function</v>
+      </c>
+      <c r="D27" t="str" s="185">
+        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E27" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F27" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B28" t="str" s="185">
+        <v>interior_cover_type</v>
+      </c>
+      <c r="C28" t="str" s="185">
+        <v>bathroom_remodel_mode</v>
+      </c>
+      <c r="D28" t="str" s="185">
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E28" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F28" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B29" t="str" s="185">
+        <v>exterior_cover_type</v>
+      </c>
+      <c r="C29" t="str" s="185">
+        <v>frame_type,survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+      </c>
+      <c r="D29" t="str" s="185">
+        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E29" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F29" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B30" t="str" s="185">
+        <v>survey_cover_top</v>
+      </c>
+      <c r="C30" t="str" s="185"/>
+      <c r="D30" t="str" s="185">
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E30" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F30" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B31" t="str" s="185">
+        <v>survey_cover_bottom</v>
+      </c>
+      <c r="C31" t="str" s="185"/>
+      <c r="D31" t="str" s="185">
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E31" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F31" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str" s="184">
+        <v>フロー</v>
+      </c>
+      <c r="B32" t="str" s="185">
+        <v>survey_cover_side</v>
+      </c>
+      <c r="C32" t="str" s="185"/>
+      <c r="D32" t="str" s="185">
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E32" t="str" s="186">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F32" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13151,371 +13771,356 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="70" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="178" t="str">
-        <x:v>01_入力フロー｜浴室仕様</x:v>
-      </x:c>
-      <x:c r="B1" s="178"/>
-      <x:c r="C1" s="178"/>
-      <x:c r="D1" s="178"/>
-      <x:c r="E1" s="178"/>
-    </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="181" t="str">
-        <x:v>順序</x:v>
-      </x:c>
-      <x:c r="B3" s="182" t="str">
-        <x:v>表示項目</x:v>
-      </x:c>
-      <x:c r="C3" s="182" t="str">
-        <x:v>データキー</x:v>
-      </x:c>
-      <x:c r="D3" s="182" t="str">
-        <x:v>候補/入力</x:v>
-      </x:c>
-      <x:c r="E3" s="183" t="str">
-        <x:v>制御</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="184" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="185" t="str">
-        <x:v>取替方式</x:v>
-      </x:c>
-      <x:c r="C4" s="185" t="str">
-        <x:v>installation_system_id</x:v>
-      </x:c>
-      <x:c r="D4" s="185" t="str">
-        <x:v>RPL_DIRECT</x:v>
-      </x:c>
-      <x:c r="E4" s="186" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="184" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="185" t="str">
-        <x:v>仕様区分</x:v>
-      </x:c>
-      <x:c r="C5" s="185" t="str">
-        <x:v>variation_id</x:v>
-      </x:c>
-      <x:c r="D5" s="185" t="str">
-        <x:v>RPL_BATH</x:v>
-      </x:c>
-      <x:c r="E5" s="186" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="184" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="185" t="str">
-        <x:v>浴室改修モード</x:v>
-      </x:c>
-      <x:c r="C6" s="185" t="str">
-        <x:v>bathroom_remodel_mode</x:v>
-      </x:c>
-      <x:c r="D6" s="185" t="str">
-        <x:v>SB同時交換 / 窓単独交換</x:v>
-      </x:c>
-      <x:c r="E6" s="186" t="str">
-        <x:v>浴室現調と連動</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="184" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="185" t="str">
-        <x:v>既設開口パターン</x:v>
-      </x:c>
-      <x:c r="C7" s="185" t="str">
-        <x:v>bathroom_opening_pattern</x:v>
-      </x:c>
-      <x:c r="D7" s="185" t="str">
-        <x:v>全面/片寄左右/くり抜き</x:v>
-      </x:c>
-      <x:c r="E7" s="186" t="str">
-        <x:v>SB同時交換時</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="184" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="185" t="str">
-        <x:v>開口構成</x:v>
-      </x:c>
-      <x:c r="C8" s="185" t="str">
-        <x:v>opening_configuration</x:v>
-      </x:c>
-      <x:c r="D8" s="185" t="str">
-        <x:v>単窓/開口縮小/連窓/段窓</x:v>
-      </x:c>
-      <x:c r="E8" s="186" t="str">
-        <x:v>必要時表示</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="184" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B9" s="185" t="str">
-        <x:v>窓種</x:v>
-      </x:c>
-      <x:c r="C9" s="185" t="str">
-        <x:v>window_type_id</x:v>
-      </x:c>
-      <x:c r="D9" s="185" t="str">
-        <x:v>浴室8窓種</x:v>
-      </x:c>
-      <x:c r="E9" s="186" t="str">
-        <x:v>条件で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="184" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="185" t="str">
-        <x:v>枠</x:v>
-      </x:c>
-      <x:c r="C10" s="185" t="str">
-        <x:v>frame_type</x:v>
-      </x:c>
-      <x:c r="D10" s="185" t="str">
-        <x:v>標準 / ブリッジ</x:v>
-      </x:c>
-      <x:c r="E10" s="186" t="str">
-        <x:v>引違いのみブリッジ表示</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="184" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="185" t="str">
-        <x:v>窓種固有仕様</x:v>
-      </x:c>
-      <x:c r="C11" s="185" t="str">
-        <x:v>window_specific</x:v>
-      </x:c>
-      <x:c r="D11" s="185" t="str">
-        <x:v>操作方式・建数等</x:v>
-      </x:c>
-      <x:c r="E11" s="186" t="str">
-        <x:v>引違い2枚建固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="184" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" s="185" t="str">
-        <x:v>採寸W/H</x:v>
-      </x:c>
-      <x:c r="C12" s="185" t="str">
-        <x:v>survey_w / survey_h</x:v>
-      </x:c>
-      <x:c r="D12" s="185" t="str">
-        <x:v>現場入力</x:v>
-      </x:c>
-      <x:c r="E12" s="186" t="str">
-        <x:v>3点採寸</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="184" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B13" s="185" t="str">
-        <x:v>出来寸W/H</x:v>
-      </x:c>
-      <x:c r="C13" s="185" t="str">
-        <x:v>finished_w / finished_h</x:v>
-      </x:c>
-      <x:c r="D13" s="185" t="str">
-        <x:v>自動算出</x:v>
-      </x:c>
-      <x:c r="E13" s="186" t="str">
-        <x:v>WD=WS-10 / HD=HS-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="184" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" s="185" t="str">
-        <x:v>外観色</x:v>
-      </x:c>
-      <x:c r="C14" s="185" t="str">
-        <x:v>sash_exterior_color</x:v>
-      </x:c>
-      <x:c r="D14" s="185" t="str">
-        <x:v>5色</x:v>
-      </x:c>
-      <x:c r="E14" s="186" t="str">
-        <x:v>公式色</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="184" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" s="185" t="str">
-        <x:v>内観色</x:v>
-      </x:c>
-      <x:c r="C15" s="185" t="str">
-        <x:v>sash_interior_color</x:v>
-      </x:c>
-      <x:c r="D15" s="185" t="str">
-        <x:v>ブラック/プレシャスホワイトP</x:v>
-      </x:c>
-      <x:c r="E15" s="186" t="str">
-        <x:v>外観と自由組合せ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="184" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B16" s="185" t="str">
-        <x:v>網戸</x:v>
-      </x:c>
-      <x:c r="C16" s="185" t="str">
-        <x:v>screen_configuration</x:v>
-      </x:c>
-      <x:c r="D16" s="185" t="str">
-        <x:v>窓種別形式</x:v>
-      </x:c>
-      <x:c r="E16" s="186" t="str">
-        <x:v>FIX非表示</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="184" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B17" s="185" t="str">
-        <x:v>ネット</x:v>
-      </x:c>
-      <x:c r="C17" s="185" t="str">
-        <x:v>screen_mesh</x:v>
-      </x:c>
-      <x:c r="D17" s="185" t="str">
-        <x:v>標準/きれい/虫イヤ/ペット</x:v>
-      </x:c>
-      <x:c r="E17" s="186" t="str">
-        <x:v>網戸形式で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="184" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B18" s="185" t="str">
-        <x:v>ガラス大分類</x:v>
-      </x:c>
-      <x:c r="C18" s="185" t="str">
-        <x:v>glass_category</x:v>
-      </x:c>
-      <x:c r="D18" s="185" t="str">
-        <x:v>一般複層/Low-E複層/トリプル</x:v>
-      </x:c>
-      <x:c r="E18" s="186" t="str">
-        <x:v>トリプルはDHFSのみ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="184" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B19" s="185" t="str">
-        <x:v>ガラス詳細</x:v>
-      </x:c>
-      <x:c r="C19" s="185" t="str">
-        <x:v>glass_detail</x:v>
-      </x:c>
-      <x:c r="D19" s="185" t="str">
-        <x:v>色・仕上げ・追加機能</x:v>
-      </x:c>
-      <x:c r="E19" s="186" t="str">
-        <x:v>条件絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="184" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B20" s="185" t="str">
-        <x:v>中空層/スペーサー</x:v>
-      </x:c>
-      <x:c r="C20" s="185" t="str">
-        <x:v>gas/spacer</x:v>
-      </x:c>
-      <x:c r="D20" s="185" t="str">
-        <x:v>公式組合せ</x:v>
-      </x:c>
-      <x:c r="E20" s="186" t="str">
-        <x:v>ブリッジは樹脂スペーサー固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="184" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B21" s="185" t="str">
-        <x:v>オプション</x:v>
-      </x:c>
-      <x:c r="C21" s="185" t="str">
-        <x:v>option_id</x:v>
-      </x:c>
-      <x:c r="D21" s="185" t="str">
-        <x:v>浴室適用品のみ</x:v>
-      </x:c>
-      <x:c r="E21" s="186" t="str">
-        <x:v>依存ルール</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="187" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B22" s="188" t="str">
-        <x:v>浴室現場・施工判定</x:v>
-      </x:c>
-      <x:c r="C22" s="188" t="str">
-        <x:v>bathroom/survey/installation_condition</x:v>
-      </x:c>
-      <x:c r="D22" s="188" t="str">
-        <x:v>別UI</x:v>
-      </x:c>
-      <x:c r="E22" s="189" t="str">
-        <x:v>商品仕様と分離</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="70" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" t="str" s="178">
+        <v>リプラス住宅用・グローバルセレクションフロー</v>
+      </c>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" t="str" s="181">
+        <v>順番</v>
+      </c>
+      <c r="B3" t="str" s="182">
+        <v>表示項目</v>
+      </c>
+      <c r="C3" t="str" s="182">
+        <v>データキー</v>
+      </c>
+      <c r="D3" t="str" s="182">
+        <v>候補/入力</v>
+      </c>
+      <c r="E3" t="str" s="183">
+        <v>制御方針</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="184">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str" s="185">
+        <v>商品・リプラス仕様</v>
+      </c>
+      <c r="C4" t="str" s="185">
+        <v>product / specification</v>
+      </c>
+      <c r="D4" t="str" s="185">
+        <v>リプラス住宅用 → 仕様</v>
+      </c>
+      <c r="E4" t="str" s="186">
+        <v>今回承認されたアプリ運用ルール</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="184">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str" s="185">
+        <v>設置・施工条件</v>
+      </c>
+      <c r="C5" t="str" s="185">
+        <v>context</v>
+      </c>
+      <c r="D5" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E5" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="184">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str" s="185">
+        <v>窓種・基本仕様</v>
+      </c>
+      <c r="C6" t="str" s="185">
+        <v>opening</v>
+      </c>
+      <c r="D6" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E6" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="184">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str" s="185">
+        <v>本体色</v>
+      </c>
+      <c r="C7" t="str" s="185">
+        <v>finish</v>
+      </c>
+      <c r="D7" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E7" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="184">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str" s="185">
+        <v>網戸</v>
+      </c>
+      <c r="C8" t="str" s="185">
+        <v>screen</v>
+      </c>
+      <c r="D8" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E8" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="184">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str" s="185">
+        <v>ガラス</v>
+      </c>
+      <c r="C9" t="str" s="185">
+        <v>glazing</v>
+      </c>
+      <c r="D9" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E9" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="184">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str" s="185">
+        <v>室内側の仕上げ・アングルカバー</v>
+      </c>
+      <c r="C10" t="str" s="185">
+        <v>interior_finish</v>
+      </c>
+      <c r="D10" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E10" t="str" s="186">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="184">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str" s="185">
+        <v>室外側の仕上げ・化粧カバー</v>
+      </c>
+      <c r="C11" t="str" s="185">
+        <v>exterior_finish</v>
+      </c>
+      <c r="D11" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E11" t="str" s="186">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="184">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str" s="185">
+        <v>新設サッシのオプション</v>
+      </c>
+      <c r="C12" t="str" s="185">
+        <v>native_options</v>
+      </c>
+      <c r="D12" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E12" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="184">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str" s="185">
+        <v>追加部材・オプション</v>
+      </c>
+      <c r="C13" t="str" s="185">
+        <v>options</v>
+      </c>
+      <c r="D13" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E13" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="184">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str" s="185">
+        <v>選択した部材の仕様</v>
+      </c>
+      <c r="C14" t="str" s="185">
+        <v>part_detail</v>
+      </c>
+      <c r="D14" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E14" t="str" s="186">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="184">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str" s="185">
+        <v>現場採寸・取付条件</v>
+      </c>
+      <c r="C15" t="str" s="185">
+        <v>survey</v>
+      </c>
+      <c r="D15" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E15" t="str" s="186">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="184">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str" s="185">
+        <v>製品寸法</v>
+      </c>
+      <c r="C16" t="str" s="185">
+        <v>size</v>
+      </c>
+      <c r="D16" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E16" t="str" s="186">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="184"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="186"/>
+      <c r="F17"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="184"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
+      <c r="E18" s="186"/>
+      <c r="F18"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="184"/>
+      <c r="B19" s="185"/>
+      <c r="C19" s="185"/>
+      <c r="D19" s="185"/>
+      <c r="E19" s="186"/>
+      <c r="F19"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="184"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="186"/>
+      <c r="F20"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="184"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="185"/>
+      <c r="D21" s="185"/>
+      <c r="E21" s="186"/>
+      <c r="F21"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="187"/>
+      <c r="B22" s="188"/>
+      <c r="C22" s="188"/>
+      <c r="D22" s="188"/>
+      <c r="E22" s="189"/>
+      <c r="F22"/>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>

--- a/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
@@ -1291,7 +1291,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1311,7 +1311,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1329,7 +1329,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1349,7 +1349,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1369,7 +1369,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1389,7 +1389,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1409,7 +1409,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1429,7 +1429,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1447,7 +1447,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1467,7 +1467,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1487,7 +1487,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1505,7 +1505,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1525,7 +1525,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1543,7 +1543,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1563,7 +1563,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1581,7 +1581,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1599,7 +1599,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1617,7 +1617,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1637,7 +1637,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1657,7 +1657,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1677,7 +1677,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1697,7 +1697,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1717,7 +1717,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1737,7 +1737,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1757,7 +1757,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1777,7 +1777,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1797,7 +1797,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1809,13 +1809,13 @@
       </c>
       <c r="C30" t="str" s="185"/>
       <c r="D30" t="str" s="185">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E30" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1827,13 +1827,13 @@
       </c>
       <c r="C31" t="str" s="185"/>
       <c r="D31" t="str" s="185">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E31" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1845,13 +1845,13 @@
       </c>
       <c r="C32" t="str" s="185"/>
       <c r="D32" t="str" s="185">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E32" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -13966,10 +13966,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="str" s="185">
-        <v>新設サッシのオプション</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C12" t="str" s="185">
-        <v>native_options</v>
+        <v>options</v>
       </c>
       <c r="D12" t="str" s="185">
         <v>選択・確認</v>
@@ -13984,71 +13984,41 @@
         <v>10</v>
       </c>
       <c r="B13" t="str" s="185">
-        <v>追加部材・オプション</v>
+        <v>製品寸法</v>
       </c>
       <c r="C13" t="str" s="185">
-        <v>options</v>
+        <v>size</v>
       </c>
       <c r="D13" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E13" t="str" s="186">
-        <v>対応する項目のみ表示</v>
+        <v>採寸後に再評価</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14">
-      <c r="A14" t="n" s="184">
-        <v>11</v>
-      </c>
-      <c r="B14" t="str" s="185">
-        <v>選択した部材の仕様</v>
-      </c>
-      <c r="C14" t="str" s="185">
-        <v>part_detail</v>
-      </c>
-      <c r="D14" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E14" t="str" s="186">
-        <v>対応する項目のみ表示</v>
-      </c>
+      <c r="A14" s="184"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="186"/>
       <c r="F14"/>
     </row>
     <row r="15">
-      <c r="A15" t="n" s="184">
-        <v>12</v>
-      </c>
-      <c r="B15" t="str" s="185">
-        <v>現場採寸・取付条件</v>
-      </c>
-      <c r="C15" t="str" s="185">
-        <v>survey</v>
-      </c>
-      <c r="D15" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E15" t="str" s="186">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A15" s="184"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
+      <c r="E15" s="186"/>
       <c r="F15"/>
     </row>
     <row r="16">
-      <c r="A16" t="n" s="184">
-        <v>13</v>
-      </c>
-      <c r="B16" t="str" s="185">
-        <v>製品寸法</v>
-      </c>
-      <c r="C16" t="str" s="185">
-        <v>size</v>
-      </c>
-      <c r="D16" t="str" s="185">
-        <v>選択・確認</v>
-      </c>
-      <c r="E16" t="str" s="186">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A16" s="184"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="186"/>
       <c r="F16"/>
     </row>
     <row r="17">

--- a/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
@@ -1276,7 +1276,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str" s="184">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B3" t="str" s="185">
         <v>exterior_cover_color</v>
@@ -1291,12 +1291,12 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str" s="184">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B4" t="str" s="185">
         <v>interior_cover_color</v>
@@ -1311,45 +1311,45 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str" s="184">
-        <v>フロー</v>
+        <v>NUMERIC_INPUT_PAIRS</v>
       </c>
       <c r="B5" t="str" s="185">
-        <v>window_type</v>
+        <v>dimension_basis</v>
       </c>
       <c r="C5" t="str" s="185"/>
       <c r="D5" t="str" s="185">
-        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
+        <v>{"basisField": "dimension_basis", "measuredBasis": "SURVEY", "finishedBasis": "FINISHED", "legacyBasis": "FINISHED", "evaluationAssignments": {"size_mode": "CUSTOM"}, "pairs": [{"measuredField": "survey_width", "finishedField": "custom_width", "offset": -10, "message": "公式換算：仕上がり寸法 = 採寸寸法 − 10mm。"}, {"measuredField": "survey_height", "finishedField": "custom_height", "offset": -10, "message": "公式換算：仕上がり寸法 = 採寸寸法 − 10mm。"}]}</v>
       </c>
       <c r="E5" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str" s="184">
-        <v>フロー</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B6" t="str" s="185">
-        <v>frame_type</v>
+        <v>inner_fit_required_component</v>
       </c>
       <c r="C6" t="str" s="185">
-        <v>window_type</v>
+        <v>installation_method</v>
       </c>
       <c r="D6" t="str" s="185">
-        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
+        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "BATH-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "BATH-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。"}</v>
       </c>
       <c r="E6" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1357,19 +1357,17 @@
         <v>フロー</v>
       </c>
       <c r="B7" t="str" s="185">
-        <v>spec_panel_configuration</v>
-      </c>
-      <c r="C7" t="str" s="185">
         <v>window_type</v>
       </c>
+      <c r="C7" t="str" s="185"/>
       <c r="D7" t="str" s="185">
-        <v>{"label": "建数", "group": "opening", "internal": false}</v>
+        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
       </c>
       <c r="E7" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1377,19 +1375,19 @@
         <v>フロー</v>
       </c>
       <c r="B8" t="str" s="185">
-        <v>spec_sash_configuration</v>
+        <v>frame_type</v>
       </c>
       <c r="C8" t="str" s="185">
         <v>window_type</v>
       </c>
       <c r="D8" t="str" s="185">
-        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
+        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
       </c>
       <c r="E8" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1397,19 +1395,19 @@
         <v>フロー</v>
       </c>
       <c r="B9" t="str" s="185">
-        <v>spec_operation_type</v>
+        <v>spec_panel_configuration</v>
       </c>
       <c r="C9" t="str" s="185">
         <v>window_type</v>
       </c>
       <c r="D9" t="str" s="185">
-        <v>{"label": "操作方式", "group": "opening", "internal": false}</v>
+        <v>{"label": "建数", "group": "opening", "internal": false}</v>
       </c>
       <c r="E9" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1417,19 +1415,19 @@
         <v>フロー</v>
       </c>
       <c r="B10" t="str" s="185">
-        <v>screen</v>
+        <v>spec_sash_configuration</v>
       </c>
       <c r="C10" t="str" s="185">
         <v>window_type</v>
       </c>
       <c r="D10" t="str" s="185">
-        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
+        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
       </c>
       <c r="E10" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1437,17 +1435,19 @@
         <v>フロー</v>
       </c>
       <c r="B11" t="str" s="185">
-        <v>size_mode</v>
-      </c>
-      <c r="C11" t="str" s="185"/>
+        <v>spec_operation_type</v>
+      </c>
+      <c r="C11" t="str" s="185">
+        <v>window_type</v>
+      </c>
       <c r="D11" t="str" s="185">
-        <v>{"label": "寸法の指定方法", "group": "size", "internal": false}</v>
+        <v>{"label": "操作方式", "group": "opening", "internal": false}</v>
       </c>
       <c r="E11" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1455,19 +1455,19 @@
         <v>フロー</v>
       </c>
       <c r="B12" t="str" s="185">
-        <v>custom_width</v>
+        <v>screen</v>
       </c>
       <c r="C12" t="str" s="185">
-        <v>size_mode</v>
+        <v>window_type</v>
       </c>
       <c r="D12" t="str" s="185">
-        <v>{"label": "製品仕上がり幅 W（mm）", "group": "size", "internal": false}</v>
+        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
       </c>
       <c r="E12" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1475,19 +1475,17 @@
         <v>フロー</v>
       </c>
       <c r="B13" t="str" s="185">
-        <v>custom_height</v>
-      </c>
-      <c r="C13" t="str" s="185">
         <v>size_mode</v>
       </c>
+      <c r="C13" t="str" s="185"/>
       <c r="D13" t="str" s="185">
-        <v>{"label": "製品仕上がり高さ H（mm）", "group": "size", "internal": false}</v>
+        <v>{"label": "寸法の指定方法", "group": "size", "internal": true}</v>
       </c>
       <c r="E13" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1505,7 +1503,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1525,7 +1523,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1543,7 +1541,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1563,7 +1561,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1581,7 +1579,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1599,7 +1597,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1617,7 +1615,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1637,7 +1635,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1657,7 +1655,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1677,7 +1675,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1697,7 +1695,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1717,7 +1715,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1737,7 +1735,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1757,7 +1755,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1777,7 +1775,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1797,7 +1795,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1805,17 +1803,19 @@
         <v>フロー</v>
       </c>
       <c r="B30" t="str" s="185">
-        <v>survey_cover_top</v>
-      </c>
-      <c r="C30" t="str" s="185"/>
+        <v>installation_method</v>
+      </c>
+      <c r="C30" t="str" s="185">
+        <v>window_type</v>
+      </c>
       <c r="D30" t="str" s="185">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "内はめ仕様", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E30" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1823,17 +1823,19 @@
         <v>フロー</v>
       </c>
       <c r="B31" t="str" s="185">
-        <v>survey_cover_bottom</v>
-      </c>
-      <c r="C31" t="str" s="185"/>
+        <v>inner_fit_required_component</v>
+      </c>
+      <c r="C31" t="str" s="185">
+        <v>installation_method</v>
+      </c>
       <c r="D31" t="str" s="185">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E31" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1841,17 +1843,97 @@
         <v>フロー</v>
       </c>
       <c r="B32" t="str" s="185">
-        <v>survey_cover_side</v>
+        <v>dimension_basis</v>
       </c>
       <c r="C32" t="str" s="185"/>
       <c r="D32" t="str" s="185">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "入力する寸法", "group": "size", "internal": false}</v>
       </c>
       <c r="E32" t="str" s="186">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B33" t="str">
+        <v>survey_width</v>
+      </c>
+      <c r="C33" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D33" t="str">
+        <v>{"label": "採寸幅 WS（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E33" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F33" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B34" t="str">
+        <v>survey_height</v>
+      </c>
+      <c r="C34" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D34" t="str">
+        <v>{"label": "採寸高さ HS（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E34" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F34" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B35" t="str">
+        <v>custom_width</v>
+      </c>
+      <c r="C35" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D35" t="str">
+        <v>{"label": "製品仕上がり幅 WD（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E35" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F35" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B36" t="str">
+        <v>custom_height</v>
+      </c>
+      <c r="C36" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D36" t="str">
+        <v>{"label": "製品仕上がり高さ HD（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E36" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F36" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -1875,7 +1957,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="178" t="str">
+      <c r="A1" t="str" s="178">
         <v>90_Evidence｜浴室仕様 根拠管理</v>
       </c>
       <c r="B1" s="178"/>
@@ -1888,7 +1970,7 @@
       <c r="I1" s="178"/>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="179" t="str">
+      <c r="A2" t="str" s="179">
         <v>推測値は登録せず、2026業務用資料・現行Web・商品カタログを突合。</v>
       </c>
       <c r="B2" s="179"/>
@@ -1900,487 +1982,480 @@
       <c r="H2" s="179"/>
       <c r="I2" s="179"/>
     </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="181" t="str">
+      <c r="A4" t="str" s="181">
         <v>evidence_id</v>
       </c>
-      <c r="B4" s="182" t="str">
+      <c r="B4" t="str" s="182">
         <v>情報源種別</v>
       </c>
-      <c r="C4" s="182" t="str">
+      <c r="C4" t="str" s="182">
         <v>資料名</v>
       </c>
-      <c r="D4" s="182" t="str">
+      <c r="D4" t="str" s="182">
         <v>発行年月</v>
       </c>
-      <c r="E4" s="182" t="str">
+      <c r="E4" t="str" s="182">
         <v>ページ/箇所</v>
       </c>
-      <c r="F4" s="182" t="str">
+      <c r="F4" t="str" s="182">
         <v>URL</v>
       </c>
-      <c r="G4" s="182" t="str">
+      <c r="G4" t="str" s="182">
         <v>確認日</v>
       </c>
-      <c r="H4" s="182" t="str">
+      <c r="H4" t="str" s="182">
         <v>確度</v>
       </c>
-      <c r="I4" s="183" t="str">
+      <c r="I4" t="str" s="183">
         <v>根拠内容</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="184" t="str">
+      <c r="A5" t="str" s="184">
         <v>BATH-EV-001</v>
       </c>
-      <c r="B5" s="185" t="str">
+      <c r="B5" t="str" s="185">
         <v>共通仕様</v>
       </c>
-      <c r="C5" s="185" t="str">
+      <c r="C5" t="str" s="185">
         <v>サッシ商品マスター共通仕様書_v0.1</v>
       </c>
-      <c r="D5" s="185" t="str">
+      <c r="D5" t="str" s="185">
         <v>2026-08-30更新</v>
       </c>
-      <c r="E5" s="185" t="str">
+      <c r="E5" t="str" s="185">
         <v>§31-34ほか</v>
       </c>
-      <c r="F5" s="185" t="str">
+      <c r="F5" t="str" s="185">
         <v>https://docs.google.com/document/d/1MfixkbV1cZ__DtBknEKsix_nnrXQqjc-LZtXUHwJv_A/edit</v>
       </c>
-      <c r="G5" s="185" t="str">
+      <c r="G5" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H5" s="185" t="str">
+      <c r="H5" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I5" s="186" t="str">
+      <c r="I5" t="str" s="186">
         <v>条件判定・Evidence・特殊案件</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="184" t="str">
+      <c r="A6" t="str" s="184">
         <v>BATH-EV-002</v>
       </c>
-      <c r="B6" s="185" t="str">
+      <c r="B6" t="str" s="185">
         <v>業務用資料集</v>
       </c>
-      <c r="C6" s="185" t="str">
+      <c r="C6" t="str" s="185">
         <v>リプラス・リプラスマンション用 取替窓 業務用資料集</v>
       </c>
-      <c r="D6" s="185" t="str">
+      <c r="D6" t="str" s="185">
         <v>2026-04</v>
       </c>
-      <c r="E6" s="185" t="str">
+      <c r="E6" t="str" s="185">
         <v>浴室仕様 p52～</v>
       </c>
-      <c r="F6" s="185" t="str">
+      <c r="F6" t="str" s="185">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G6" s="185" t="str">
+      <c r="G6" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H6" s="185" t="str">
+      <c r="H6" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I6" s="186" t="str">
+      <c r="I6" t="str" s="186">
         <v>浴室商品体系・価格表</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="184" t="str">
+      <c r="A7" t="str" s="184">
         <v>BATH-EV-003</v>
       </c>
-      <c r="B7" s="185" t="str">
+      <c r="B7" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C7" s="185" t="str">
+      <c r="C7" t="str" s="185">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D7" s="185" t="str">
+      <c r="D7" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E7" s="185" t="str">
+      <c r="E7" t="str" s="185">
         <v>p30-32</v>
       </c>
-      <c r="F7" s="185" t="str">
+      <c r="F7" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G7" s="185" t="str">
+      <c r="G7" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H7" s="185" t="str">
+      <c r="H7" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I7" s="186" t="str">
+      <c r="I7" t="str" s="186">
         <v>改修モード・8窓種・開口縮小・色</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="184" t="str">
+      <c r="A8" t="str" s="184">
         <v>BATH-EV-004</v>
       </c>
-      <c r="B8" s="185" t="str">
+      <c r="B8" t="str" s="185">
         <v>公式Web</v>
       </c>
-      <c r="C8" s="185" t="str">
+      <c r="C8" t="str" s="185">
         <v>LIXIL リプラス 浴室仕様</v>
       </c>
-      <c r="D8" s="185" t="str">
+      <c r="D8" t="str" s="185">
         <v>現行</v>
       </c>
-      <c r="E8" s="185" t="str">
+      <c r="E8" t="str" s="185">
         <v>品種/色/ガラス/網戸</v>
       </c>
-      <c r="F8" s="185" t="str">
+      <c r="F8" t="str" s="185">
         <v>https://www.lixil.co.jp/lineup/window/replus/variation/bathroom/</v>
       </c>
-      <c r="G8" s="185" t="str">
+      <c r="G8" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H8" s="185" t="str">
+      <c r="H8" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I8" s="186" t="str">
+      <c r="I8" t="str" s="186">
         <v>現行品種・既設樹脂/木不可・トリプル注記</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="184" t="str">
+      <c r="A9" t="str" s="184">
         <v>BATH-EV-005</v>
       </c>
-      <c r="B9" s="185" t="str">
+      <c r="B9" t="str" s="185">
         <v>業務用資料集</v>
       </c>
-      <c r="C9" s="185" t="str">
+      <c r="C9" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D9" s="185" t="str">
+      <c r="D9" t="str" s="185">
         <v>2026-04</v>
       </c>
-      <c r="E9" s="185" t="str">
+      <c r="E9" t="str" s="185">
         <v>浴室仕様 完成品価格表</v>
       </c>
-      <c r="F9" s="185" t="str">
+      <c r="F9" t="str" s="185">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G9" s="185" t="str">
+      <c r="G9" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H9" s="185" t="str">
+      <c r="H9" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I9" s="186" t="str">
+      <c r="I9" t="str" s="186">
         <v>窓種別網戸・ガラス・部材・依存</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="184" t="str">
+      <c r="A10" t="str" s="184">
         <v>BATH-EV-006</v>
       </c>
-      <c r="B10" s="185" t="str">
+      <c r="B10" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C10" s="185" t="str">
+      <c r="C10" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D10" s="185" t="str">
+      <c r="D10" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E10" s="185" t="str">
+      <c r="E10" t="str" s="185">
         <v>p100</v>
       </c>
-      <c r="F10" s="185" t="str">
+      <c r="F10" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G10" s="185" t="str">
+      <c r="G10" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H10" s="185" t="str">
+      <c r="H10" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I10" s="186" t="str">
+      <c r="I10" t="str" s="186">
         <v>引違い標準/ブリッジ寸法・A/B/C/D・式</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="184" t="str">
+      <c r="A11" t="str" s="184">
         <v>BATH-EV-007</v>
       </c>
-      <c r="B11" s="185" t="str">
+      <c r="B11" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C11" s="185" t="str">
+      <c r="C11" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D11" s="185" t="str">
+      <c r="D11" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E11" s="185" t="str">
+      <c r="E11" t="str" s="185">
         <v>p112</v>
       </c>
-      <c r="F11" s="185" t="str">
+      <c r="F11" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G11" s="185" t="str">
+      <c r="G11" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H11" s="185" t="str">
+      <c r="H11" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I11" s="186" t="str">
+      <c r="I11" t="str" s="186">
         <v>装飾窓/上げ下げFS寸法・重量・清掃アーム</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="184" t="str">
+      <c r="A12" t="str" s="184">
         <v>BATH-EV-008</v>
       </c>
-      <c r="B12" s="185" t="str">
+      <c r="B12" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C12" s="185" t="str">
+      <c r="C12" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D12" s="185" t="str">
+      <c r="D12" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E12" s="185" t="str">
+      <c r="E12" t="str" s="185">
         <v>p113</v>
       </c>
-      <c r="F12" s="185" t="str">
+      <c r="F12" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G12" s="185" t="str">
+      <c r="G12" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H12" s="185" t="str">
+      <c r="H12" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I12" s="186" t="str">
+      <c r="I12" t="str" s="186">
         <v>FIX・連窓・段窓・断熱パネル・総W式</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="184" t="str">
+      <c r="A13" t="str" s="184">
         <v>BATH-EV-009</v>
       </c>
-      <c r="B13" s="185" t="str">
+      <c r="B13" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C13" s="185" t="str">
+      <c r="C13" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D13" s="185" t="str">
+      <c r="D13" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E13" s="185" t="str">
+      <c r="E13" t="str" s="185">
         <v>p205-211/現調資料</v>
       </c>
-      <c r="F13" s="185" t="str">
+      <c r="F13" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G13" s="185" t="str">
+      <c r="G13" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H13" s="185" t="str">
+      <c r="H13" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I13" s="186" t="str">
+      <c r="I13" t="str" s="186">
         <v>SB同時/窓単独・3点採寸・補強金具・見付・防水条件</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="184" t="str">
+      <c r="A14" t="str" s="184">
         <v>BATH-EV-010</v>
       </c>
-      <c r="B14" s="185" t="str">
+      <c r="B14" t="str" s="185">
         <v>商品カタログ</v>
       </c>
-      <c r="C14" s="185" t="str">
+      <c r="C14" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D14" s="185" t="str">
+      <c r="D14" t="str" s="185">
         <v>2025-08</v>
       </c>
-      <c r="E14" s="185" t="str">
+      <c r="E14" t="str" s="185">
         <v>p48/p55付近</v>
       </c>
-      <c r="F14" s="185" t="str">
+      <c r="F14" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G14" s="185" t="str">
+      <c r="G14" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H14" s="185" t="str">
+      <c r="H14" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I14" s="186" t="str">
+      <c r="I14" t="str" s="186">
         <v>複層/トリプルガラス体系・中空層・スペーサー</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="184" t="str">
+      <c r="A15" t="str" s="184">
         <v>BATH-EV-011</v>
       </c>
-      <c r="B15" s="185" t="str">
+      <c r="B15" t="str" s="185">
         <v>商品カタログ/業務用資料</v>
       </c>
-      <c r="C15" s="185" t="str">
+      <c r="C15" t="str" s="185">
         <v>同上</v>
       </c>
-      <c r="D15" s="185" t="str">
+      <c r="D15" t="str" s="185">
         <v>2025-08/2026-04</v>
       </c>
-      <c r="E15" s="185" t="str">
+      <c r="E15" t="str" s="185">
         <v>有償品取付可否/浴室各価格表</v>
       </c>
-      <c r="F15" s="185" t="str">
+      <c r="F15" t="str" s="185">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G15" s="185" t="str">
+      <c r="G15" t="str" s="185">
         <v>2026-08-31</v>
       </c>
-      <c r="H15" s="185" t="str">
+      <c r="H15" t="str" s="185">
         <v>HIGH</v>
       </c>
-      <c r="I15" s="186" t="str">
+      <c r="I15" t="str" s="186">
         <v>有償品・併用不可・浴室不可OP</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="187" t="str">
+      <c r="A16" t="str" s="187">
         <v>BATH-EV-012</v>
       </c>
-      <c r="B16" s="188" t="str">
+      <c r="B16" t="str" s="188">
         <v>商品カタログ</v>
       </c>
-      <c r="C16" s="188" t="str">
+      <c r="C16" t="str" s="188">
         <v>同上</v>
       </c>
-      <c r="D16" s="188" t="str">
+      <c r="D16" t="str" s="188">
         <v>2025-08</v>
       </c>
-      <c r="E16" s="188" t="str">
+      <c r="E16" t="str" s="188">
         <v>p206/連段・ガラス制限</v>
       </c>
-      <c r="F16" s="188" t="str">
+      <c r="F16" t="str" s="188">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G16" s="188" t="str">
+      <c r="G16" t="str" s="188">
         <v>2026-08-31</v>
       </c>
-      <c r="H16" s="188" t="str">
+      <c r="H16" t="str" s="188">
         <v>HIGH</v>
       </c>
-      <c r="I16" s="189" t="str">
+      <c r="I16" t="str" s="189">
         <v>無目露出不可・特殊複合・ガラス/耐荷重</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>DELTA-SPACER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B17" s="36" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E17" s="36" t="inlineStr">
-        <is>
-          <t>PDF 52,104,116,120</t>
-        </is>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G17" s="36" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H17" s="36" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I17" s="37" t="inlineStr">
-        <is>
-          <t>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A17" t="str" s="35">
+        <v>DELTA-SPACER-EV-V4</v>
+      </c>
+      <c r="B17" t="str" s="36">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C17" t="str" s="36">
+        <v>IS9800</v>
+      </c>
+      <c r="D17" t="str" s="36">
+        <v>2026-10</v>
+      </c>
+      <c r="E17" t="str" s="36">
+        <v>PDF 52,104,116,120</v>
+      </c>
+      <c r="F17" t="str" s="36">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G17" t="str" s="36">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H17" t="str" s="36">
+        <v>HIGH</v>
+      </c>
+      <c r="I17" t="str" s="37">
+        <v>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>DELTA-BATH-TABLE-EV-V4</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E18" s="36" t="inlineStr">
-        <is>
-          <t>PDF 95,96</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G18" s="36" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H18" s="36" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I18" s="37" t="inlineStr">
-        <is>
-          <t>SOURCE_PRICE_BAND_CORRECTION_NO_SIZE_RULE_PATCH / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A18" t="str" s="35">
+        <v>DELTA-BATH-TABLE-EV-V4</v>
+      </c>
+      <c r="B18" t="str" s="36">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C18" t="str" s="36">
+        <v>IS9800</v>
+      </c>
+      <c r="D18" t="str" s="36">
+        <v>2026-10</v>
+      </c>
+      <c r="E18" t="str" s="36">
+        <v>PDF 95,96</v>
+      </c>
+      <c r="F18" t="str" s="36">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G18" t="str" s="36">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H18" t="str" s="36">
+        <v>HIGH</v>
+      </c>
+      <c r="I18" t="str" s="37">
+        <v>SOURCE_PRICE_BAND_CORRECTION_NO_SIZE_RULE_PATCH / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="37"/>
+      <c r="A19" t="str" s="35">
+        <v>EV-DIMENSIONS-INNER-FIT-V11</v>
+      </c>
+      <c r="B19" t="str" s="36">
+        <v>公式商品カタログ</v>
+      </c>
+      <c r="C19" t="str" s="36">
+        <v>リプラス SN1200</v>
+      </c>
+      <c r="D19" t="str" s="36">
+        <v>2025-08</v>
+      </c>
+      <c r="E19" t="str" s="36">
+        <v>PDF252/254・231/233/247/249/251</v>
+      </c>
+      <c r="F19" t="str" s="36">
+        <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
+      </c>
+      <c r="G19" t="str" s="36">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H19" t="str" s="36">
+        <v>HIGH</v>
+      </c>
+      <c r="I19" t="str" s="37">
+        <v>採寸/出来寸の相互換算と標準/内はめの施工仕様を共通Runtimeへ接続</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="38"/>
@@ -13831,7 +13906,7 @@
         <v>リプラス住宅用 → 仕様</v>
       </c>
       <c r="E4" t="str" s="186">
-        <v>今回承認されたアプリ運用ルール</v>
+        <v>アプリ運用ルール</v>
       </c>
       <c r="F4"/>
     </row>
@@ -13930,16 +14005,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="str" s="185">
-        <v>室内側の仕上げ・アングルカバー</v>
+        <v>内はめ仕様</v>
       </c>
       <c r="C10" t="str" s="185">
-        <v>interior_finish</v>
+        <v>inner_fit</v>
       </c>
       <c r="D10" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E10" t="str" s="186">
-        <v>本体色に連動</v>
+        <v>ガラスの後で選択</v>
       </c>
       <c r="F10"/>
     </row>
@@ -13948,16 +14023,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="str" s="185">
-        <v>室外側の仕上げ・化粧カバー</v>
+        <v>室内側の仕上げ・アングルカバー</v>
       </c>
       <c r="C11" t="str" s="185">
-        <v>exterior_finish</v>
+        <v>interior_finish</v>
       </c>
       <c r="D11" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E11" t="str" s="186">
-        <v>本体色に連動</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F11"/>
     </row>
@@ -13966,10 +14041,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="str" s="185">
-        <v>追加部材・オプション</v>
+        <v>室外側の仕上げ・化粧カバー</v>
       </c>
       <c r="C12" t="str" s="185">
-        <v>options</v>
+        <v>exterior_finish</v>
       </c>
       <c r="D12" t="str" s="185">
         <v>選択・確認</v>
@@ -13984,25 +14059,35 @@
         <v>10</v>
       </c>
       <c r="B13" t="str" s="185">
-        <v>製品寸法</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C13" t="str" s="185">
-        <v>size</v>
+        <v>options</v>
       </c>
       <c r="D13" t="str" s="185">
         <v>選択・確認</v>
       </c>
       <c r="E13" t="str" s="186">
-        <v>採寸後に再評価</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14">
-      <c r="A14" s="184"/>
-      <c r="B14" s="185"/>
-      <c r="C14" s="185"/>
-      <c r="D14" s="185"/>
-      <c r="E14" s="186"/>
+      <c r="A14" t="n" s="184">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str" s="185">
+        <v>製品寸法</v>
+      </c>
+      <c r="C14" t="str" s="185">
+        <v>size</v>
+      </c>
+      <c r="D14" t="str" s="185">
+        <v>選択・確認</v>
+      </c>
+      <c r="E14" t="str" s="186">
+        <v>採寸と仕上がりを併記</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15">

--- a/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
@@ -1291,7 +1291,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1311,7 +1311,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1329,7 +1329,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1343,13 +1343,13 @@
         <v>installation_method</v>
       </c>
       <c r="D6" t="str" s="185">
-        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "BATH-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "BATH-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。"}</v>
+        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "BATH-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "BATH-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。", "resolvedNoticeVisibility": "INTERNAL_ONLY"}</v>
       </c>
       <c r="E6" t="str" s="186">
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1367,7 +1367,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1387,7 +1387,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1407,7 +1407,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1427,7 +1427,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1447,7 +1447,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1467,7 +1467,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1485,7 +1485,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1503,7 +1503,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1517,13 +1517,13 @@
         <v>sash_exterior_color</v>
       </c>
       <c r="D15" t="str" s="185">
-        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E15" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1541,7 +1541,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1555,13 +1555,13 @@
         <v>sash_interior_color</v>
       </c>
       <c r="D17" t="str" s="185">
-        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E17" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1579,7 +1579,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1597,7 +1597,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1615,7 +1615,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1635,7 +1635,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1655,7 +1655,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1675,7 +1675,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1695,7 +1695,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1715,7 +1715,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1735,7 +1735,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1755,7 +1755,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1775,7 +1775,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1795,7 +1795,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1815,7 +1815,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1829,13 +1829,13 @@
         <v>installation_method</v>
       </c>
       <c r="D31" t="str" s="185">
-        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": false}</v>
+        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E31" t="str" s="186">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1853,7 +1853,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1873,7 +1873,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -1893,7 +1893,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -1913,7 +1913,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="36">
@@ -1933,7 +1933,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F36" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
   </sheetData>

--- a/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_BATH.xlsx
@@ -1291,7 +1291,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1311,7 +1311,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1329,7 +1329,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1349,7 +1349,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1367,7 +1367,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1387,7 +1387,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1407,7 +1407,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1427,7 +1427,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1447,7 +1447,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1467,7 +1467,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1485,7 +1485,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1503,7 +1503,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1523,7 +1523,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1541,7 +1541,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1561,7 +1561,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1579,7 +1579,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1597,7 +1597,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1615,7 +1615,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1629,13 +1629,13 @@
         <v>frame_type,installation_region,window_type</v>
       </c>
       <c r="D21" t="str" s="185">
-        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false, "rank": 1}</v>
       </c>
       <c r="E21" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1646,16 +1646,16 @@
         <v>glass</v>
       </c>
       <c r="C22" t="str" s="185">
-        <v>frame_type,glass_category,installation_region,window_type</v>
+        <v>frame_type,glass_appearance,glass_category,installation_region,window_type</v>
       </c>
       <c r="D22" t="str" s="185">
-        <v>{"label": "ガラス詳細・Low-E仕様", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス詳細・Low-E仕様", "group": "glazing", "internal": false, "rank": 3}</v>
       </c>
       <c r="E22" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1675,7 +1675,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1695,7 +1695,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1715,7 +1715,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1726,16 +1726,16 @@
         <v>glass_function</v>
       </c>
       <c r="C26" t="str" s="185">
-        <v>glass_category,glass,window_type</v>
+        <v>glass_category,glass_appearance,glass,window_type</v>
       </c>
       <c r="D26" t="str" s="185">
-        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false, "rank": 4}</v>
       </c>
       <c r="E26" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1746,16 +1746,16 @@
         <v>glass_appearance</v>
       </c>
       <c r="C27" t="str" s="185">
-        <v>glass,glass_function</v>
+        <v>glass_category</v>
       </c>
       <c r="D27" t="str" s="185">
-        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス種", "group": "glazing", "internal": false, "rank": 2}</v>
       </c>
       <c r="E27" t="str" s="186">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1775,7 +1775,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1795,7 +1795,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1815,7 +1815,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1835,7 +1835,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1853,7 +1853,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1873,7 +1873,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -1893,7 +1893,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -1913,7 +1913,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="36">
@@ -1933,7 +1933,67 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F36" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B37" t="str">
+        <v>glass_appearance</v>
+      </c>
+      <c r="C37" t="str">
+        <v>glass_category</v>
+      </c>
+      <c r="D37" t="str">
+        <v>{"key": "glass_appearance", "displayLabel": "ガラス種", "dataType": "ENUM", "displayOrder": 710, "required": false, "autoSelectSingle": false, "parentFields": ["glass_category"], "selector": {"glass_category": {"$exists": true}}, "choices": [{"value": "MILKY", "displayLabel": "乳白", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "CLEAR", "displayLabel": "透明", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 1}, {"value": "OBSCURE", "displayLabel": "型板", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "FROST", "displayLabel": "フロスト", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}]}</v>
+      </c>
+      <c r="E37" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F37" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B38" t="str">
+        <v>glass</v>
+      </c>
+      <c r="C38" t="str">
+        <v>frame_type,glass_appearance,glass_category,installation_region,window_type</v>
+      </c>
+      <c r="D38" t="str">
+        <v>{"key": "glass", "displayLabel": "ガラス詳細・Low-E仕様", "dataType": "ENUM", "displayOrder": 720, "choices": [{"value": "BATH-GL-GENERAL", "displayLabel": "一般複層ガラス", "evidenceIds": ["BATH-EV-004,010"], "selector": {"window_type": {"$exists": true}, "frame_type": "BATH-STD", "glass_category": "GENERAL_DOUBLE"}, "metadata": {"manualCheck": true}}, {"value": "BATH-GL-LOWE-CLEAR", "displayLabel": "Low-E複層 クリア", "evidenceIds": ["BATH-EV-004,010"], "selector": {"window_type": {"$exists": true}, "frame_type": {"$exists": true}, "glass_category": "LOW_E_DOUBLE"}, "metadata": {"manualCheck": true}}, {"value": "BATH-GL-LOWE-GREEN", "displayLabel": "Low-E複層 グリーン", "evidenceIds": ["BATH-EV-004,010"], "selector": {"window_type": {"$exists": true}, "frame_type": {"$exists": true}, "glass_category": "LOW_E_DOUBLE"}, "metadata": {"manualCheck": true}}, {"value": "BATH-GL-LOWE-HS", "displayLabel": "Low-E複層 グリーン（高遮熱仕様）", "evidenceIds": ["BATH-EV-004,010"], "selector": {"window_type": {"$exists": true}, "frame_type": {"$exists": true}, "glass_category": "LOW_E_DOUBLE"}, "metadata": {"manualCheck": true}}, {"value": "BATH-GL-LOWE-BRONZE", "displayLabel": "Low-E複層 ブロンズ", "evidenceIds": ["BATH-EV-010"], "selector": {"window_type": {"$exists": true}, "frame_type": {"$exists": true}, "installation_region": {"$in": ["北海道", "東北"]}, "glass_category": "LOW_E_DOUBLE"}, "metadata": {"manualCheck": true}}, {"value": "BATH-GL-T-CC", "displayLabel": "トリプル クリア×クリア", "evidenceIds": ["BATH-EV-004,010"], "selector": {"window_type": "RPL_BATH_DHFS", "frame_type": {"$exists": true}, "glass_category": "TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "BATH-GL-T-GG", "displayLabel": "トリプル グリーン×グリーン", "evidenceIds": ["BATH-EV-004,010"], "selector": {"window_type": "RPL_BATH_DHFS", "frame_type": {"$exists": true}, "glass_category": "TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "BATH-GL-T-CG", "displayLabel": "トリプル クリア×グリーン", "evidenceIds": ["BATH-EV-010"], "selector": {"window_type": "RPL_BATH_DHFS", "frame_type": {"$exists": true}, "glass_category": "TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "BATH-GL-T-CB", "displayLabel": "トリプル クリア×ブロンズ", "evidenceIds": ["BATH-EV-010"], "selector": {"window_type": "RPL_BATH_DHFS", "frame_type": {"$exists": true}, "installation_region": {"$in": ["北海道", "東北"]}, "glass_category": "TRIPLE"}, "metadata": {"manualCheck": true}}], "required": false, "autoSelectSingle": false, "parentFields": ["frame_type", "glass_appearance", "glass_category", "installation_region", "window_type"], "selector": {"glass_category": {"$exists": true}}}</v>
+      </c>
+      <c r="E38" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F38" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B39" t="str">
+        <v>glass_function</v>
+      </c>
+      <c r="C39" t="str">
+        <v>glass_category,glass_appearance,glass,window_type</v>
+      </c>
+      <c r="D39" t="str">
+        <v>{"key": "glass_function", "displayLabel": "ガラス追加機能", "dataType": "ENUM", "displayOrder": 730, "required": false, "autoSelectSingle": false, "parentFields": ["glass_category", "glass_appearance", "glass", "window_type"], "selector": {"glass": {"$exists": true}}, "choices": [{"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "GENERAL_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "GENERAL_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "DISASTER", "displayLabel": "防災安全合わせ", "selector": {"all": [{"glass_category": "GENERAL_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "GENERAL_DOUBLE", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "GRID", "displayLabel": "格子入り", "selector": {"all": [{"glass_category": "GENERAL_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 5}, {"value": "BLIND", "displayLabel": "ブラインドインPG", "selector": {"all": [{"glass_category": "GENERAL_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 6}, {"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "LOW_E_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "LOW_E_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "DISASTER", "displayLabel": "防災安全合わせ", "selector": {"all": [{"glass_category": "LOW_E_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "LOW_E_DOUBLE", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "GRID", "displayLabel": "格子入り", "selector": {"all": [{"glass_category": "LOW_E_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 5}, {"value": "BLIND", "displayLabel": "ブラインドインPG", "selector": {"all": [{"glass_category": "LOW_E_DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 6}, {"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "DISASTER", "displayLabel": "防災安全合わせ", "selector": {"all": [{"glass_category": "TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "TRIPLE", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "THIN", "displayLabel": "特殊薄板合わせ", "selector": {"all": [{"glass_category": "TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 7}]}</v>
+      </c>
+      <c r="E39" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F39" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
   </sheetData>
